--- a/portfolio-projects/01-data-quality-excel-reporting/data/raw/orders_raw.xlsx
+++ b/portfolio-projects/01-data-quality-excel-reporting/data/raw/orders_raw.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="orders_raw" sheetId="1" r:id="Ra2fd656175e04653"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="orders_raw" sheetId="1" r:id="R35f09fed0863472c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,6 +13,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+  </x:numFmts>
   <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
@@ -63,7 +66,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="11">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -82,6 +85,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -353,7 +359,7 @@
       <x:c r="A2" s="9" t="n">
         <x:v>1001</x:v>
       </x:c>
-      <x:c r="B2" s="9" t="n">
+      <x:c r="B2" s="10" t="n">
         <x:v>46115</x:v>
       </x:c>
       <x:c r="C2" s="9" t="str">
@@ -385,7 +391,7 @@
       <x:c r="A3" s="9" t="n">
         <x:v>1002</x:v>
       </x:c>
-      <x:c r="B3" s="9" t="n">
+      <x:c r="B3" s="10" t="n">
         <x:v>46153</x:v>
       </x:c>
       <x:c r="C3" s="9" t="str">
@@ -417,7 +423,7 @@
       <x:c r="A4" s="9" t="n">
         <x:v>1003</x:v>
       </x:c>
-      <x:c r="B4" s="9" t="n">
+      <x:c r="B4" s="10" t="n">
         <x:v>46164</x:v>
       </x:c>
       <x:c r="C4" s="9" t="str">
@@ -449,7 +455,7 @@
       <x:c r="A5" s="9" t="n">
         <x:v>1004</x:v>
       </x:c>
-      <x:c r="B5" s="9" t="n">
+      <x:c r="B5" s="10" t="n">
         <x:v>46047</x:v>
       </x:c>
       <x:c r="C5" s="9" t="str">
@@ -481,7 +487,7 @@
       <x:c r="A6" s="9" t="n">
         <x:v>1005</x:v>
       </x:c>
-      <x:c r="B6" s="9" t="n">
+      <x:c r="B6" s="10" t="n">
         <x:v>46100</x:v>
       </x:c>
       <x:c r="C6" s="9" t="str">
@@ -513,7 +519,7 @@
       <x:c r="A7" s="9" t="n">
         <x:v>1006</x:v>
       </x:c>
-      <x:c r="B7" s="9" t="n">
+      <x:c r="B7" s="10" t="n">
         <x:v>46153</x:v>
       </x:c>
       <x:c r="C7" s="9" t="str">
@@ -545,7 +551,7 @@
       <x:c r="A8" s="9" t="n">
         <x:v>1007</x:v>
       </x:c>
-      <x:c r="B8" s="9" t="n">
+      <x:c r="B8" s="10" t="n">
         <x:v>46131</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
@@ -577,7 +583,7 @@
       <x:c r="A9" s="9" t="n">
         <x:v>1007</x:v>
       </x:c>
-      <x:c r="B9" s="9" t="n">
+      <x:c r="B9" s="10" t="n">
         <x:v>46101</x:v>
       </x:c>
       <x:c r="C9" s="9" t="str">
@@ -609,7 +615,7 @@
       <x:c r="A10" s="9" t="n">
         <x:v>1009</x:v>
       </x:c>
-      <x:c r="B10" s="9" t="n">
+      <x:c r="B10" s="10" t="n">
         <x:v>46111</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
@@ -641,7 +647,7 @@
       <x:c r="A11" s="9" t="n">
         <x:v>1010</x:v>
       </x:c>
-      <x:c r="B11" s="9" t="n">
+      <x:c r="B11" s="10" t="n">
         <x:v>46108</x:v>
       </x:c>
       <x:c r="C11" s="9" t="str">
@@ -673,7 +679,7 @@
       <x:c r="A12" s="9" t="n">
         <x:v>1011</x:v>
       </x:c>
-      <x:c r="B12" s="9" t="n">
+      <x:c r="B12" s="10" t="n">
         <x:v>46084</x:v>
       </x:c>
       <x:c r="C12" s="9" t="str">
@@ -705,7 +711,7 @@
       <x:c r="A13" s="9" t="n">
         <x:v>1012</x:v>
       </x:c>
-      <x:c r="B13" s="9" t="n">
+      <x:c r="B13" s="10" t="n">
         <x:v>46170</x:v>
       </x:c>
       <x:c r="C13" s="9" t="str">
@@ -737,7 +743,7 @@
       <x:c r="A14" s="9" t="n">
         <x:v>1013</x:v>
       </x:c>
-      <x:c r="B14" s="9" t="n">
+      <x:c r="B14" s="10" t="n">
         <x:v>46057</x:v>
       </x:c>
       <x:c r="C14" s="9" t="str">
@@ -769,7 +775,7 @@
       <x:c r="A15" s="9" t="n">
         <x:v>1014</x:v>
       </x:c>
-      <x:c r="B15" s="9" t="n">
+      <x:c r="B15" s="10" t="n">
         <x:v>46145</x:v>
       </x:c>
       <x:c r="C15" s="9" t="str">
@@ -801,7 +807,7 @@
       <x:c r="A16" s="9" t="n">
         <x:v>1015</x:v>
       </x:c>
-      <x:c r="B16" s="9" t="n">
+      <x:c r="B16" s="10" t="n">
         <x:v>46092</x:v>
       </x:c>
       <x:c r="C16" s="9" t="str">
@@ -833,7 +839,7 @@
       <x:c r="A17" s="9" t="n">
         <x:v>1016</x:v>
       </x:c>
-      <x:c r="B17" s="9" t="n">
+      <x:c r="B17" s="10" t="n">
         <x:v>46134</x:v>
       </x:c>
       <x:c r="C17" s="9" t="str"/>
@@ -863,7 +869,7 @@
       <x:c r="A18" s="9" t="n">
         <x:v>1017</x:v>
       </x:c>
-      <x:c r="B18" s="9" t="n">
+      <x:c r="B18" s="10" t="n">
         <x:v>46091</x:v>
       </x:c>
       <x:c r="C18" s="9" t="str">
@@ -895,7 +901,7 @@
       <x:c r="A19" s="9" t="n">
         <x:v>1018</x:v>
       </x:c>
-      <x:c r="B19" s="9" t="n">
+      <x:c r="B19" s="10" t="n">
         <x:v>46116</x:v>
       </x:c>
       <x:c r="C19" s="9" t="str">
@@ -927,7 +933,7 @@
       <x:c r="A20" s="9" t="n">
         <x:v>1019</x:v>
       </x:c>
-      <x:c r="B20" s="9" t="n">
+      <x:c r="B20" s="10" t="n">
         <x:v>46172</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
@@ -959,7 +965,7 @@
       <x:c r="A21" s="9" t="n">
         <x:v>1020</x:v>
       </x:c>
-      <x:c r="B21" s="9" t="n">
+      <x:c r="B21" s="10" t="n">
         <x:v>46038</x:v>
       </x:c>
       <x:c r="C21" s="9" t="str">
@@ -991,7 +997,7 @@
       <x:c r="A22" s="9" t="n">
         <x:v>1021</x:v>
       </x:c>
-      <x:c r="B22" s="9" t="n">
+      <x:c r="B22" s="10" t="n">
         <x:v>46164</x:v>
       </x:c>
       <x:c r="C22" s="9" t="str">
@@ -1023,7 +1029,7 @@
       <x:c r="A23" s="9" t="n">
         <x:v>1022</x:v>
       </x:c>
-      <x:c r="B23" s="9" t="n">
+      <x:c r="B23" s="10" t="n">
         <x:v>46043</x:v>
       </x:c>
       <x:c r="C23" s="9" t="str">
@@ -1055,7 +1061,7 @@
       <x:c r="A24" s="9" t="n">
         <x:v>1023</x:v>
       </x:c>
-      <x:c r="B24" s="9" t="n">
+      <x:c r="B24" s="10" t="n">
         <x:v>46133</x:v>
       </x:c>
       <x:c r="C24" s="9" t="str">
@@ -1087,7 +1093,7 @@
       <x:c r="A25" s="9" t="n">
         <x:v>1024</x:v>
       </x:c>
-      <x:c r="B25" s="9" t="n">
+      <x:c r="B25" s="10" t="n">
         <x:v>46105</x:v>
       </x:c>
       <x:c r="C25" s="9" t="str">
@@ -1119,7 +1125,7 @@
       <x:c r="A26" s="9" t="n">
         <x:v>1025</x:v>
       </x:c>
-      <x:c r="B26" s="9" t="n">
+      <x:c r="B26" s="10" t="n">
         <x:v>46173</x:v>
       </x:c>
       <x:c r="C26" s="9" t="str">
@@ -1151,7 +1157,7 @@
       <x:c r="A27" s="9" t="n">
         <x:v>1026</x:v>
       </x:c>
-      <x:c r="B27" s="9" t="n">
+      <x:c r="B27" s="10" t="n">
         <x:v>46117</x:v>
       </x:c>
       <x:c r="C27" s="9" t="str">
@@ -1183,7 +1189,7 @@
       <x:c r="A28" s="9" t="n">
         <x:v>1027</x:v>
       </x:c>
-      <x:c r="B28" s="9" t="n">
+      <x:c r="B28" s="10" t="n">
         <x:v>46034</x:v>
       </x:c>
       <x:c r="C28" s="9" t="str">
@@ -1215,7 +1221,7 @@
       <x:c r="A29" s="9" t="n">
         <x:v>1028</x:v>
       </x:c>
-      <x:c r="B29" s="9" t="n">
+      <x:c r="B29" s="10" t="n">
         <x:v>46123</x:v>
       </x:c>
       <x:c r="C29" s="9" t="str">
@@ -1247,7 +1253,7 @@
       <x:c r="A30" s="9" t="n">
         <x:v>1029</x:v>
       </x:c>
-      <x:c r="B30" s="9" t="n">
+      <x:c r="B30" s="10" t="n">
         <x:v>46111</x:v>
       </x:c>
       <x:c r="C30" s="9" t="str">
@@ -1277,7 +1283,7 @@
       <x:c r="A31" s="9" t="n">
         <x:v>1030</x:v>
       </x:c>
-      <x:c r="B31" s="9" t="n">
+      <x:c r="B31" s="10" t="n">
         <x:v>46103</x:v>
       </x:c>
       <x:c r="C31" s="9" t="str">
@@ -1309,7 +1315,7 @@
       <x:c r="A32" s="9" t="n">
         <x:v>1031</x:v>
       </x:c>
-      <x:c r="B32" s="9" t="n">
+      <x:c r="B32" s="10" t="n">
         <x:v>46027</x:v>
       </x:c>
       <x:c r="C32" s="9" t="str">
@@ -1341,7 +1347,7 @@
       <x:c r="A33" s="9" t="n">
         <x:v>1032</x:v>
       </x:c>
-      <x:c r="B33" s="9" t="n">
+      <x:c r="B33" s="10" t="n">
         <x:v>46055</x:v>
       </x:c>
       <x:c r="C33" s="9" t="str">
@@ -1373,7 +1379,7 @@
       <x:c r="A34" s="9" t="n">
         <x:v>1033</x:v>
       </x:c>
-      <x:c r="B34" s="9" t="n">
+      <x:c r="B34" s="10" t="n">
         <x:v>46067</x:v>
       </x:c>
       <x:c r="C34" s="9" t="str">
@@ -1405,7 +1411,7 @@
       <x:c r="A35" s="9" t="n">
         <x:v>1034</x:v>
       </x:c>
-      <x:c r="B35" s="9" t="n">
+      <x:c r="B35" s="10" t="n">
         <x:v>46085</x:v>
       </x:c>
       <x:c r="C35" s="9" t="str">
@@ -1437,7 +1443,7 @@
       <x:c r="A36" s="9" t="n">
         <x:v>1035</x:v>
       </x:c>
-      <x:c r="B36" s="9" t="n">
+      <x:c r="B36" s="10" t="n">
         <x:v>46062</x:v>
       </x:c>
       <x:c r="C36" s="9" t="str">
@@ -1469,7 +1475,7 @@
       <x:c r="A37" s="9" t="n">
         <x:v>1036</x:v>
       </x:c>
-      <x:c r="B37" s="9" t="n">
+      <x:c r="B37" s="10" t="n">
         <x:v>46035</x:v>
       </x:c>
       <x:c r="C37" s="9" t="str">
@@ -1501,7 +1507,7 @@
       <x:c r="A38" s="9" t="n">
         <x:v>1037</x:v>
       </x:c>
-      <x:c r="B38" s="9" t="n">
+      <x:c r="B38" s="10" t="n">
         <x:v>46075</x:v>
       </x:c>
       <x:c r="C38" s="9" t="str">
@@ -1533,7 +1539,7 @@
       <x:c r="A39" s="9" t="n">
         <x:v>1038</x:v>
       </x:c>
-      <x:c r="B39" s="9" t="n">
+      <x:c r="B39" s="10" t="n">
         <x:v>46170</x:v>
       </x:c>
       <x:c r="C39" s="9" t="str">
@@ -1565,7 +1571,7 @@
       <x:c r="A40" s="9" t="n">
         <x:v>1039</x:v>
       </x:c>
-      <x:c r="B40" s="9" t="n">
+      <x:c r="B40" s="10" t="n">
         <x:v>46035</x:v>
       </x:c>
       <x:c r="C40" s="9" t="str">
@@ -1597,7 +1603,7 @@
       <x:c r="A41" s="9" t="n">
         <x:v>1040</x:v>
       </x:c>
-      <x:c r="B41" s="9" t="n">
+      <x:c r="B41" s="10" t="n">
         <x:v>46064</x:v>
       </x:c>
       <x:c r="C41" s="9" t="str">
@@ -1629,7 +1635,7 @@
       <x:c r="A42" s="9" t="n">
         <x:v>1041</x:v>
       </x:c>
-      <x:c r="B42" s="9" t="n">
+      <x:c r="B42" s="10" t="n">
         <x:v>46118</x:v>
       </x:c>
       <x:c r="C42" s="9" t="str">
@@ -1661,7 +1667,7 @@
       <x:c r="A43" s="9" t="n">
         <x:v>1042</x:v>
       </x:c>
-      <x:c r="B43" s="9" t="n">
+      <x:c r="B43" s="10" t="n">
         <x:v>46034</x:v>
       </x:c>
       <x:c r="C43" s="9" t="str">
@@ -1693,7 +1699,7 @@
       <x:c r="A44" s="9" t="n">
         <x:v>1043</x:v>
       </x:c>
-      <x:c r="B44" s="9" t="n">
+      <x:c r="B44" s="10" t="n">
         <x:v>46087</x:v>
       </x:c>
       <x:c r="C44" s="9" t="str">
@@ -1725,7 +1731,7 @@
       <x:c r="A45" s="9" t="n">
         <x:v>1044</x:v>
       </x:c>
-      <x:c r="B45" s="9" t="n">
+      <x:c r="B45" s="10" t="n">
         <x:v>46170</x:v>
       </x:c>
       <x:c r="C45" s="9" t="str">
@@ -1757,7 +1763,7 @@
       <x:c r="A46" s="9" t="n">
         <x:v>1045</x:v>
       </x:c>
-      <x:c r="B46" s="9" t="n">
+      <x:c r="B46" s="10" t="n">
         <x:v>46121</x:v>
       </x:c>
       <x:c r="C46" s="9" t="str">
@@ -1789,7 +1795,7 @@
       <x:c r="A47" s="9" t="n">
         <x:v>1046</x:v>
       </x:c>
-      <x:c r="B47" s="9" t="n">
+      <x:c r="B47" s="10" t="n">
         <x:v>46125</x:v>
       </x:c>
       <x:c r="C47" s="9" t="str">
@@ -1821,7 +1827,7 @@
       <x:c r="A48" s="9" t="n">
         <x:v>1047</x:v>
       </x:c>
-      <x:c r="B48" s="9" t="n">
+      <x:c r="B48" s="10" t="n">
         <x:v>46156</x:v>
       </x:c>
       <x:c r="C48" s="9" t="str">
@@ -1853,7 +1859,7 @@
       <x:c r="A49" s="9" t="n">
         <x:v>1048</x:v>
       </x:c>
-      <x:c r="B49" s="9" t="n">
+      <x:c r="B49" s="10" t="n">
         <x:v>46098</x:v>
       </x:c>
       <x:c r="C49" s="9" t="str">
@@ -1885,7 +1891,7 @@
       <x:c r="A50" s="9" t="n">
         <x:v>1049</x:v>
       </x:c>
-      <x:c r="B50" s="9" t="n">
+      <x:c r="B50" s="10" t="n">
         <x:v>46110</x:v>
       </x:c>
       <x:c r="C50" s="9" t="str">
@@ -1917,7 +1923,7 @@
       <x:c r="A51" s="9" t="n">
         <x:v>1050</x:v>
       </x:c>
-      <x:c r="B51" s="9" t="n">
+      <x:c r="B51" s="10" t="n">
         <x:v>46164</x:v>
       </x:c>
       <x:c r="C51" s="9" t="str">
@@ -1949,7 +1955,7 @@
       <x:c r="A52" s="9" t="n">
         <x:v>1051</x:v>
       </x:c>
-      <x:c r="B52" s="9" t="n">
+      <x:c r="B52" s="10" t="n">
         <x:v>46126</x:v>
       </x:c>
       <x:c r="C52" s="9" t="str">
@@ -1981,7 +1987,7 @@
       <x:c r="A53" s="9" t="n">
         <x:v>1052</x:v>
       </x:c>
-      <x:c r="B53" s="9" t="n">
+      <x:c r="B53" s="10" t="n">
         <x:v>46065</x:v>
       </x:c>
       <x:c r="C53" s="9" t="str">
@@ -2013,7 +2019,7 @@
       <x:c r="A54" s="9" t="n">
         <x:v>1053</x:v>
       </x:c>
-      <x:c r="B54" s="9" t="n">
+      <x:c r="B54" s="10" t="n">
         <x:v>46052</x:v>
       </x:c>
       <x:c r="C54" s="9" t="str">
@@ -2045,7 +2051,7 @@
       <x:c r="A55" s="9" t="n">
         <x:v>1054</x:v>
       </x:c>
-      <x:c r="B55" s="9" t="n">
+      <x:c r="B55" s="10" t="n">
         <x:v>46039</x:v>
       </x:c>
       <x:c r="C55" s="9" t="str">
@@ -2077,7 +2083,7 @@
       <x:c r="A56" s="9" t="n">
         <x:v>1055</x:v>
       </x:c>
-      <x:c r="B56" s="9" t="n">
+      <x:c r="B56" s="10" t="n">
         <x:v>46126</x:v>
       </x:c>
       <x:c r="C56" s="9" t="str">
@@ -2109,7 +2115,7 @@
       <x:c r="A57" s="9" t="n">
         <x:v>1056</x:v>
       </x:c>
-      <x:c r="B57" s="9" t="n">
+      <x:c r="B57" s="10" t="n">
         <x:v>46159</x:v>
       </x:c>
       <x:c r="C57" s="9" t="str">
@@ -2141,7 +2147,7 @@
       <x:c r="A58" s="9" t="n">
         <x:v>1057</x:v>
       </x:c>
-      <x:c r="B58" s="9" t="n">
+      <x:c r="B58" s="10" t="n">
         <x:v>46163</x:v>
       </x:c>
       <x:c r="C58" s="9" t="str">
@@ -2173,7 +2179,7 @@
       <x:c r="A59" s="9" t="n">
         <x:v>1058</x:v>
       </x:c>
-      <x:c r="B59" s="9" t="n">
+      <x:c r="B59" s="10" t="n">
         <x:v>46113</x:v>
       </x:c>
       <x:c r="C59" s="9" t="str">
@@ -2205,7 +2211,7 @@
       <x:c r="A60" s="9" t="n">
         <x:v>1059</x:v>
       </x:c>
-      <x:c r="B60" s="9" t="n">
+      <x:c r="B60" s="10" t="n">
         <x:v>46084</x:v>
       </x:c>
       <x:c r="C60" s="9" t="str">
@@ -2237,7 +2243,7 @@
       <x:c r="A61" s="9" t="n">
         <x:v>1060</x:v>
       </x:c>
-      <x:c r="B61" s="9" t="n">
+      <x:c r="B61" s="10" t="n">
         <x:v>46040</x:v>
       </x:c>
       <x:c r="C61" s="9" t="str">
@@ -2269,7 +2275,7 @@
       <x:c r="A62" s="9" t="n">
         <x:v>1061</x:v>
       </x:c>
-      <x:c r="B62" s="9" t="n">
+      <x:c r="B62" s="10" t="n">
         <x:v>46155</x:v>
       </x:c>
       <x:c r="C62" s="9" t="str">
@@ -2301,7 +2307,7 @@
       <x:c r="A63" s="9" t="n">
         <x:v>1062</x:v>
       </x:c>
-      <x:c r="B63" s="9" t="n">
+      <x:c r="B63" s="10" t="n">
         <x:v>46167</x:v>
       </x:c>
       <x:c r="C63" s="9" t="str">
@@ -2333,7 +2339,7 @@
       <x:c r="A64" s="9" t="n">
         <x:v>1063</x:v>
       </x:c>
-      <x:c r="B64" s="9" t="n">
+      <x:c r="B64" s="10" t="n">
         <x:v>46171</x:v>
       </x:c>
       <x:c r="C64" s="9" t="str">
@@ -2365,7 +2371,7 @@
       <x:c r="A65" s="9" t="n">
         <x:v>1064</x:v>
       </x:c>
-      <x:c r="B65" s="9" t="n">
+      <x:c r="B65" s="10" t="n">
         <x:v>46139</x:v>
       </x:c>
       <x:c r="C65" s="9" t="str">
@@ -2397,7 +2403,7 @@
       <x:c r="A66" s="9" t="n">
         <x:v>1065</x:v>
       </x:c>
-      <x:c r="B66" s="9" t="n">
+      <x:c r="B66" s="10" t="n">
         <x:v>46136</x:v>
       </x:c>
       <x:c r="C66" s="9" t="str">
@@ -2429,7 +2435,7 @@
       <x:c r="A67" s="9" t="n">
         <x:v>1066</x:v>
       </x:c>
-      <x:c r="B67" s="9" t="n">
+      <x:c r="B67" s="10" t="n">
         <x:v>46157</x:v>
       </x:c>
       <x:c r="C67" s="9" t="str">
@@ -2461,7 +2467,7 @@
       <x:c r="A68" s="9" t="n">
         <x:v>1067</x:v>
       </x:c>
-      <x:c r="B68" s="9" t="n">
+      <x:c r="B68" s="10" t="n">
         <x:v>46055</x:v>
       </x:c>
       <x:c r="C68" s="9" t="str">
@@ -2493,7 +2499,7 @@
       <x:c r="A69" s="9" t="n">
         <x:v>1068</x:v>
       </x:c>
-      <x:c r="B69" s="9" t="n">
+      <x:c r="B69" s="10" t="n">
         <x:v>46158</x:v>
       </x:c>
       <x:c r="C69" s="9" t="str">
@@ -2525,7 +2531,7 @@
       <x:c r="A70" s="9" t="n">
         <x:v>1069</x:v>
       </x:c>
-      <x:c r="B70" s="9" t="n">
+      <x:c r="B70" s="10" t="n">
         <x:v>46160</x:v>
       </x:c>
       <x:c r="C70" s="9" t="str">
@@ -2557,7 +2563,7 @@
       <x:c r="A71" s="9" t="n">
         <x:v>1070</x:v>
       </x:c>
-      <x:c r="B71" s="9" t="n">
+      <x:c r="B71" s="10" t="n">
         <x:v>46055</x:v>
       </x:c>
       <x:c r="C71" s="9" t="str">
@@ -2589,7 +2595,7 @@
       <x:c r="A72" s="9" t="n">
         <x:v>1071</x:v>
       </x:c>
-      <x:c r="B72" s="9" t="n">
+      <x:c r="B72" s="10" t="n">
         <x:v>46100</x:v>
       </x:c>
       <x:c r="C72" s="9" t="str">
@@ -2621,7 +2627,7 @@
       <x:c r="A73" s="9" t="n">
         <x:v>1072</x:v>
       </x:c>
-      <x:c r="B73" s="9" t="n">
+      <x:c r="B73" s="10" t="n">
         <x:v>46118</x:v>
       </x:c>
       <x:c r="C73" s="9" t="str">
@@ -2653,7 +2659,7 @@
       <x:c r="A74" s="9" t="n">
         <x:v>1073</x:v>
       </x:c>
-      <x:c r="B74" s="9" t="n">
+      <x:c r="B74" s="10" t="n">
         <x:v>46075</x:v>
       </x:c>
       <x:c r="C74" s="9" t="str">
@@ -2685,7 +2691,7 @@
       <x:c r="A75" s="9" t="n">
         <x:v>1074</x:v>
       </x:c>
-      <x:c r="B75" s="9" t="n">
+      <x:c r="B75" s="10" t="n">
         <x:v>46428</x:v>
       </x:c>
       <x:c r="C75" s="9" t="str">
@@ -2717,7 +2723,7 @@
       <x:c r="A76" s="9" t="n">
         <x:v>1075</x:v>
       </x:c>
-      <x:c r="B76" s="9" t="n">
+      <x:c r="B76" s="10" t="n">
         <x:v>46168</x:v>
       </x:c>
       <x:c r="C76" s="9" t="str">
@@ -2749,7 +2755,7 @@
       <x:c r="A77" s="9" t="n">
         <x:v>1076</x:v>
       </x:c>
-      <x:c r="B77" s="9" t="n">
+      <x:c r="B77" s="10" t="n">
         <x:v>46063</x:v>
       </x:c>
       <x:c r="C77" s="9" t="str">
@@ -2781,7 +2787,7 @@
       <x:c r="A78" s="9" t="n">
         <x:v>1077</x:v>
       </x:c>
-      <x:c r="B78" s="9" t="n">
+      <x:c r="B78" s="10" t="n">
         <x:v>46129</x:v>
       </x:c>
       <x:c r="C78" s="9" t="str">
@@ -2813,7 +2819,7 @@
       <x:c r="A79" s="9" t="n">
         <x:v>1078</x:v>
       </x:c>
-      <x:c r="B79" s="9" t="n">
+      <x:c r="B79" s="10" t="n">
         <x:v>46033</x:v>
       </x:c>
       <x:c r="C79" s="9" t="str">
@@ -2845,7 +2851,7 @@
       <x:c r="A80" s="9" t="n">
         <x:v>1079</x:v>
       </x:c>
-      <x:c r="B80" s="9" t="n">
+      <x:c r="B80" s="10" t="n">
         <x:v>46064</x:v>
       </x:c>
       <x:c r="C80" s="9" t="str">
@@ -2877,7 +2883,7 @@
       <x:c r="A81" s="9" t="n">
         <x:v>1080</x:v>
       </x:c>
-      <x:c r="B81" s="9" t="n">
+      <x:c r="B81" s="10" t="n">
         <x:v>46060</x:v>
       </x:c>
       <x:c r="C81" s="9" t="str">
@@ -2909,7 +2915,7 @@
       <x:c r="A82" s="9" t="n">
         <x:v>1081</x:v>
       </x:c>
-      <x:c r="B82" s="9" t="n">
+      <x:c r="B82" s="10" t="n">
         <x:v>46064</x:v>
       </x:c>
       <x:c r="C82" s="9" t="str">
@@ -2941,7 +2947,7 @@
       <x:c r="A83" s="9" t="n">
         <x:v>1082</x:v>
       </x:c>
-      <x:c r="B83" s="9" t="n">
+      <x:c r="B83" s="10" t="n">
         <x:v>46168</x:v>
       </x:c>
       <x:c r="C83" s="9" t="str">
@@ -2973,7 +2979,7 @@
       <x:c r="A84" s="9" t="n">
         <x:v>1083</x:v>
       </x:c>
-      <x:c r="B84" s="9" t="n">
+      <x:c r="B84" s="10" t="n">
         <x:v>46141</x:v>
       </x:c>
       <x:c r="C84" s="9" t="str">
@@ -3005,7 +3011,7 @@
       <x:c r="A85" s="9" t="n">
         <x:v>1084</x:v>
       </x:c>
-      <x:c r="B85" s="9" t="n">
+      <x:c r="B85" s="10" t="n">
         <x:v>46043</x:v>
       </x:c>
       <x:c r="C85" s="9" t="str">
@@ -3037,7 +3043,7 @@
       <x:c r="A86" s="9" t="n">
         <x:v>1085</x:v>
       </x:c>
-      <x:c r="B86" s="9" t="n">
+      <x:c r="B86" s="10" t="n">
         <x:v>46166</x:v>
       </x:c>
       <x:c r="C86" s="9" t="str">
@@ -3069,7 +3075,7 @@
       <x:c r="A87" s="9" t="n">
         <x:v>1086</x:v>
       </x:c>
-      <x:c r="B87" s="9" t="n">
+      <x:c r="B87" s="10" t="n">
         <x:v>46171</x:v>
       </x:c>
       <x:c r="C87" s="9" t="str">
@@ -3101,7 +3107,7 @@
       <x:c r="A88" s="9" t="n">
         <x:v>1087</x:v>
       </x:c>
-      <x:c r="B88" s="9" t="n">
+      <x:c r="B88" s="10" t="n">
         <x:v>46098</x:v>
       </x:c>
       <x:c r="C88" s="9" t="str">
@@ -3133,7 +3139,7 @@
       <x:c r="A89" s="9" t="n">
         <x:v>1088</x:v>
       </x:c>
-      <x:c r="B89" s="9" t="n">
+      <x:c r="B89" s="10" t="n">
         <x:v>46120</x:v>
       </x:c>
       <x:c r="C89" s="9" t="str">
@@ -3165,7 +3171,7 @@
       <x:c r="A90" s="9" t="n">
         <x:v>1089</x:v>
       </x:c>
-      <x:c r="B90" s="9" t="n">
+      <x:c r="B90" s="10" t="n">
         <x:v>46072</x:v>
       </x:c>
       <x:c r="C90" s="9" t="str">
@@ -3197,7 +3203,7 @@
       <x:c r="A91" s="9" t="n">
         <x:v>1090</x:v>
       </x:c>
-      <x:c r="B91" s="9" t="n">
+      <x:c r="B91" s="10" t="n">
         <x:v>46124</x:v>
       </x:c>
       <x:c r="C91" s="9" t="str">
@@ -3229,7 +3235,7 @@
       <x:c r="A92" s="9" t="n">
         <x:v>1091</x:v>
       </x:c>
-      <x:c r="B92" s="9" t="n">
+      <x:c r="B92" s="10" t="n">
         <x:v>46030</x:v>
       </x:c>
       <x:c r="C92" s="9" t="str">
@@ -3261,7 +3267,7 @@
       <x:c r="A93" s="9" t="n">
         <x:v>1092</x:v>
       </x:c>
-      <x:c r="B93" s="9" t="n">
+      <x:c r="B93" s="10" t="n">
         <x:v>46119</x:v>
       </x:c>
       <x:c r="C93" s="9" t="str">
@@ -3293,7 +3299,7 @@
       <x:c r="A94" s="9" t="n">
         <x:v>1093</x:v>
       </x:c>
-      <x:c r="B94" s="9" t="n">
+      <x:c r="B94" s="10" t="n">
         <x:v>46110</x:v>
       </x:c>
       <x:c r="C94" s="9" t="str">
@@ -3325,7 +3331,7 @@
       <x:c r="A95" s="9" t="n">
         <x:v>1094</x:v>
       </x:c>
-      <x:c r="B95" s="9" t="n">
+      <x:c r="B95" s="10" t="n">
         <x:v>46126</x:v>
       </x:c>
       <x:c r="C95" s="9" t="str">
@@ -3357,7 +3363,7 @@
       <x:c r="A96" s="9" t="n">
         <x:v>1095</x:v>
       </x:c>
-      <x:c r="B96" s="9" t="n">
+      <x:c r="B96" s="10" t="n">
         <x:v>46127</x:v>
       </x:c>
       <x:c r="C96" s="9" t="str">
@@ -3389,7 +3395,7 @@
       <x:c r="A97" s="9" t="n">
         <x:v>1096</x:v>
       </x:c>
-      <x:c r="B97" s="9" t="n">
+      <x:c r="B97" s="10" t="n">
         <x:v>46039</x:v>
       </x:c>
       <x:c r="C97" s="9" t="str">
@@ -3421,7 +3427,7 @@
       <x:c r="A98" s="9" t="n">
         <x:v>1097</x:v>
       </x:c>
-      <x:c r="B98" s="9" t="n">
+      <x:c r="B98" s="10" t="n">
         <x:v>46108</x:v>
       </x:c>
       <x:c r="C98" s="9" t="str">
@@ -3453,7 +3459,7 @@
       <x:c r="A99" s="9" t="n">
         <x:v>1098</x:v>
       </x:c>
-      <x:c r="B99" s="9" t="n">
+      <x:c r="B99" s="10" t="n">
         <x:v>46151</x:v>
       </x:c>
       <x:c r="C99" s="9" t="str">
@@ -3485,7 +3491,7 @@
       <x:c r="A100" s="9" t="n">
         <x:v>1099</x:v>
       </x:c>
-      <x:c r="B100" s="9" t="n">
+      <x:c r="B100" s="10" t="n">
         <x:v>46077</x:v>
       </x:c>
       <x:c r="C100" s="9" t="str">
@@ -3517,7 +3523,7 @@
       <x:c r="A101" s="9" t="n">
         <x:v>1100</x:v>
       </x:c>
-      <x:c r="B101" s="9" t="n">
+      <x:c r="B101" s="10" t="n">
         <x:v>46050</x:v>
       </x:c>
       <x:c r="C101" s="9" t="str">
@@ -3549,7 +3555,7 @@
       <x:c r="A102" s="9" t="n">
         <x:v>1101</x:v>
       </x:c>
-      <x:c r="B102" s="9" t="n">
+      <x:c r="B102" s="10" t="n">
         <x:v>46138</x:v>
       </x:c>
       <x:c r="C102" s="9" t="str">
@@ -3581,7 +3587,7 @@
       <x:c r="A103" s="9" t="n">
         <x:v>1102</x:v>
       </x:c>
-      <x:c r="B103" s="9" t="n">
+      <x:c r="B103" s="10" t="n">
         <x:v>46043</x:v>
       </x:c>
       <x:c r="C103" s="9" t="str">
@@ -3613,7 +3619,7 @@
       <x:c r="A104" s="9" t="n">
         <x:v>1103</x:v>
       </x:c>
-      <x:c r="B104" s="9" t="n">
+      <x:c r="B104" s="10" t="n">
         <x:v>46112</x:v>
       </x:c>
       <x:c r="C104" s="9" t="str">
@@ -3645,7 +3651,7 @@
       <x:c r="A105" s="9" t="n">
         <x:v>1104</x:v>
       </x:c>
-      <x:c r="B105" s="9" t="n">
+      <x:c r="B105" s="10" t="n">
         <x:v>46045</x:v>
       </x:c>
       <x:c r="C105" s="9" t="str">
@@ -3677,7 +3683,7 @@
       <x:c r="A106" s="9" t="n">
         <x:v>1105</x:v>
       </x:c>
-      <x:c r="B106" s="9" t="n">
+      <x:c r="B106" s="10" t="n">
         <x:v>46069</x:v>
       </x:c>
       <x:c r="C106" s="9" t="str">
@@ -3709,7 +3715,7 @@
       <x:c r="A107" s="9" t="n">
         <x:v>1106</x:v>
       </x:c>
-      <x:c r="B107" s="9" t="n">
+      <x:c r="B107" s="10" t="n">
         <x:v>46114</x:v>
       </x:c>
       <x:c r="C107" s="9" t="str">
@@ -3741,7 +3747,7 @@
       <x:c r="A108" s="9" t="n">
         <x:v>1107</x:v>
       </x:c>
-      <x:c r="B108" s="9" t="n">
+      <x:c r="B108" s="10" t="n">
         <x:v>46112</x:v>
       </x:c>
       <x:c r="C108" s="9" t="str">
@@ -3773,7 +3779,7 @@
       <x:c r="A109" s="9" t="n">
         <x:v>1108</x:v>
       </x:c>
-      <x:c r="B109" s="9" t="n">
+      <x:c r="B109" s="10" t="n">
         <x:v>46085</x:v>
       </x:c>
       <x:c r="C109" s="9" t="str">
@@ -3805,7 +3811,7 @@
       <x:c r="A110" s="9" t="n">
         <x:v>1109</x:v>
       </x:c>
-      <x:c r="B110" s="9" t="n">
+      <x:c r="B110" s="10" t="n">
         <x:v>46165</x:v>
       </x:c>
       <x:c r="C110" s="9" t="str">
@@ -3837,7 +3843,7 @@
       <x:c r="A111" s="9" t="n">
         <x:v>1110</x:v>
       </x:c>
-      <x:c r="B111" s="9" t="n">
+      <x:c r="B111" s="10" t="n">
         <x:v>46102</x:v>
       </x:c>
       <x:c r="C111" s="9" t="str">
@@ -3869,7 +3875,7 @@
       <x:c r="A112" s="9" t="n">
         <x:v>1111</x:v>
       </x:c>
-      <x:c r="B112" s="9" t="n">
+      <x:c r="B112" s="10" t="n">
         <x:v>46052</x:v>
       </x:c>
       <x:c r="C112" s="9" t="str">
@@ -3901,7 +3907,7 @@
       <x:c r="A113" s="9" t="n">
         <x:v>1112</x:v>
       </x:c>
-      <x:c r="B113" s="9" t="n">
+      <x:c r="B113" s="10" t="n">
         <x:v>46105</x:v>
       </x:c>
       <x:c r="C113" s="9" t="str">
@@ -3933,7 +3939,7 @@
       <x:c r="A114" s="9" t="n">
         <x:v>1113</x:v>
       </x:c>
-      <x:c r="B114" s="9" t="n">
+      <x:c r="B114" s="10" t="n">
         <x:v>46037</x:v>
       </x:c>
       <x:c r="C114" s="9" t="str">
@@ -3965,7 +3971,7 @@
       <x:c r="A115" s="9" t="n">
         <x:v>1114</x:v>
       </x:c>
-      <x:c r="B115" s="9" t="n">
+      <x:c r="B115" s="10" t="n">
         <x:v>46062</x:v>
       </x:c>
       <x:c r="C115" s="9" t="str">
@@ -3997,7 +4003,7 @@
       <x:c r="A116" s="9" t="n">
         <x:v>1115</x:v>
       </x:c>
-      <x:c r="B116" s="9" t="n">
+      <x:c r="B116" s="10" t="n">
         <x:v>46154</x:v>
       </x:c>
       <x:c r="C116" s="9" t="str">
@@ -4029,7 +4035,7 @@
       <x:c r="A117" s="9" t="n">
         <x:v>1116</x:v>
       </x:c>
-      <x:c r="B117" s="9" t="n">
+      <x:c r="B117" s="10" t="n">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="C117" s="9" t="str">
@@ -4061,7 +4067,7 @@
       <x:c r="A118" s="9" t="n">
         <x:v>1117</x:v>
       </x:c>
-      <x:c r="B118" s="9" t="n">
+      <x:c r="B118" s="10" t="n">
         <x:v>46142</x:v>
       </x:c>
       <x:c r="C118" s="9" t="str">
@@ -4093,7 +4099,7 @@
       <x:c r="A119" s="9" t="n">
         <x:v>1118</x:v>
       </x:c>
-      <x:c r="B119" s="9" t="n">
+      <x:c r="B119" s="10" t="n">
         <x:v>46073</x:v>
       </x:c>
       <x:c r="C119" s="9" t="str">
@@ -4125,7 +4131,7 @@
       <x:c r="A120" s="9" t="n">
         <x:v>1119</x:v>
       </x:c>
-      <x:c r="B120" s="9" t="n">
+      <x:c r="B120" s="10" t="n">
         <x:v>46134</x:v>
       </x:c>
       <x:c r="C120" s="9" t="str">
@@ -4157,7 +4163,7 @@
       <x:c r="A121" s="9" t="n">
         <x:v>1120</x:v>
       </x:c>
-      <x:c r="B121" s="9" t="n">
+      <x:c r="B121" s="10" t="n">
         <x:v>46072</x:v>
       </x:c>
       <x:c r="C121" s="9" t="str">
@@ -4189,7 +4195,7 @@
       <x:c r="A122" s="9" t="n">
         <x:v>1121</x:v>
       </x:c>
-      <x:c r="B122" s="9" t="n">
+      <x:c r="B122" s="10" t="n">
         <x:v>46134</x:v>
       </x:c>
       <x:c r="C122" s="9" t="str">
@@ -4221,7 +4227,7 @@
       <x:c r="A123" s="9" t="n">
         <x:v>1122</x:v>
       </x:c>
-      <x:c r="B123" s="9" t="n">
+      <x:c r="B123" s="10" t="n">
         <x:v>46084</x:v>
       </x:c>
       <x:c r="C123" s="9" t="str">
@@ -4253,7 +4259,7 @@
       <x:c r="A124" s="9" t="n">
         <x:v>1123</x:v>
       </x:c>
-      <x:c r="B124" s="9" t="n">
+      <x:c r="B124" s="10" t="n">
         <x:v>46106</x:v>
       </x:c>
       <x:c r="C124" s="9" t="str">
@@ -4285,7 +4291,7 @@
       <x:c r="A125" s="9" t="n">
         <x:v>1124</x:v>
       </x:c>
-      <x:c r="B125" s="9" t="n">
+      <x:c r="B125" s="10" t="n">
         <x:v>46142</x:v>
       </x:c>
       <x:c r="C125" s="9" t="str">
@@ -4317,7 +4323,7 @@
       <x:c r="A126" s="9" t="n">
         <x:v>1125</x:v>
       </x:c>
-      <x:c r="B126" s="9" t="n">
+      <x:c r="B126" s="10" t="n">
         <x:v>46060</x:v>
       </x:c>
       <x:c r="C126" s="9" t="str">
@@ -4349,7 +4355,7 @@
       <x:c r="A127" s="9" t="n">
         <x:v>1126</x:v>
       </x:c>
-      <x:c r="B127" s="9" t="n">
+      <x:c r="B127" s="10" t="n">
         <x:v>46064</x:v>
       </x:c>
       <x:c r="C127" s="9" t="str">
@@ -4381,7 +4387,7 @@
       <x:c r="A128" s="9" t="n">
         <x:v>1127</x:v>
       </x:c>
-      <x:c r="B128" s="9" t="n">
+      <x:c r="B128" s="10" t="n">
         <x:v>46131</x:v>
       </x:c>
       <x:c r="C128" s="9" t="str">
@@ -4413,7 +4419,7 @@
       <x:c r="A129" s="9" t="n">
         <x:v>1128</x:v>
       </x:c>
-      <x:c r="B129" s="9" t="n">
+      <x:c r="B129" s="10" t="n">
         <x:v>46137</x:v>
       </x:c>
       <x:c r="C129" s="9" t="str">
@@ -4445,7 +4451,7 @@
       <x:c r="A130" s="9" t="n">
         <x:v>1129</x:v>
       </x:c>
-      <x:c r="B130" s="9" t="n">
+      <x:c r="B130" s="10" t="n">
         <x:v>46067</x:v>
       </x:c>
       <x:c r="C130" s="9" t="str">
@@ -4477,7 +4483,7 @@
       <x:c r="A131" s="9" t="n">
         <x:v>1130</x:v>
       </x:c>
-      <x:c r="B131" s="9" t="n">
+      <x:c r="B131" s="10" t="n">
         <x:v>46154</x:v>
       </x:c>
       <x:c r="C131" s="9" t="str">
@@ -4509,7 +4515,7 @@
       <x:c r="A132" s="9" t="n">
         <x:v>1131</x:v>
       </x:c>
-      <x:c r="B132" s="9" t="n">
+      <x:c r="B132" s="10" t="n">
         <x:v>46063</x:v>
       </x:c>
       <x:c r="C132" s="9" t="str">
@@ -4539,7 +4545,7 @@
       <x:c r="A133" s="9" t="n">
         <x:v>1132</x:v>
       </x:c>
-      <x:c r="B133" s="9" t="n">
+      <x:c r="B133" s="10" t="n">
         <x:v>46097</x:v>
       </x:c>
       <x:c r="C133" s="9" t="str">
@@ -4571,7 +4577,7 @@
       <x:c r="A134" s="9" t="n">
         <x:v>1133</x:v>
       </x:c>
-      <x:c r="B134" s="9" t="n">
+      <x:c r="B134" s="10" t="n">
         <x:v>46095</x:v>
       </x:c>
       <x:c r="C134" s="9" t="str">
@@ -4603,7 +4609,7 @@
       <x:c r="A135" s="9" t="n">
         <x:v>1134</x:v>
       </x:c>
-      <x:c r="B135" s="9" t="n">
+      <x:c r="B135" s="10" t="n">
         <x:v>46068</x:v>
       </x:c>
       <x:c r="C135" s="9" t="str">
@@ -4635,7 +4641,7 @@
       <x:c r="A136" s="9" t="n">
         <x:v>1135</x:v>
       </x:c>
-      <x:c r="B136" s="9" t="n">
+      <x:c r="B136" s="10" t="n">
         <x:v>46155</x:v>
       </x:c>
       <x:c r="C136" s="9" t="str">
@@ -4667,7 +4673,7 @@
       <x:c r="A137" s="9" t="n">
         <x:v>1136</x:v>
       </x:c>
-      <x:c r="B137" s="9" t="n">
+      <x:c r="B137" s="10" t="n">
         <x:v>46080</x:v>
       </x:c>
       <x:c r="C137" s="9" t="str">
@@ -4699,7 +4705,7 @@
       <x:c r="A138" s="9" t="n">
         <x:v>1137</x:v>
       </x:c>
-      <x:c r="B138" s="9" t="n">
+      <x:c r="B138" s="10" t="n">
         <x:v>46033</x:v>
       </x:c>
       <x:c r="C138" s="9" t="str">
@@ -4731,7 +4737,7 @@
       <x:c r="A139" s="9" t="n">
         <x:v>1138</x:v>
       </x:c>
-      <x:c r="B139" s="9" t="n">
+      <x:c r="B139" s="10" t="n">
         <x:v>46137</x:v>
       </x:c>
       <x:c r="C139" s="9" t="str">
@@ -4763,7 +4769,7 @@
       <x:c r="A140" s="9" t="n">
         <x:v>1139</x:v>
       </x:c>
-      <x:c r="B140" s="9" t="n">
+      <x:c r="B140" s="10" t="n">
         <x:v>46154</x:v>
       </x:c>
       <x:c r="C140" s="9" t="str">
@@ -4795,7 +4801,7 @@
       <x:c r="A141" s="9" t="n">
         <x:v>1140</x:v>
       </x:c>
-      <x:c r="B141" s="9" t="n">
+      <x:c r="B141" s="10" t="n">
         <x:v>46169</x:v>
       </x:c>
       <x:c r="C141" s="9" t="str">
@@ -4827,7 +4833,7 @@
       <x:c r="A142" s="9" t="n">
         <x:v>1141</x:v>
       </x:c>
-      <x:c r="B142" s="9" t="n">
+      <x:c r="B142" s="10" t="n">
         <x:v>46163</x:v>
       </x:c>
       <x:c r="C142" s="9" t="str">
@@ -4859,7 +4865,7 @@
       <x:c r="A143" s="9" t="n">
         <x:v>1142</x:v>
       </x:c>
-      <x:c r="B143" s="9" t="n">
+      <x:c r="B143" s="10" t="n">
         <x:v>46117</x:v>
       </x:c>
       <x:c r="C143" s="9" t="str">
@@ -4891,7 +4897,7 @@
       <x:c r="A144" s="9" t="n">
         <x:v>1143</x:v>
       </x:c>
-      <x:c r="B144" s="9" t="n">
+      <x:c r="B144" s="10" t="n">
         <x:v>46055</x:v>
       </x:c>
       <x:c r="C144" s="9" t="str">
@@ -4923,7 +4929,7 @@
       <x:c r="A145" s="9" t="n">
         <x:v>1144</x:v>
       </x:c>
-      <x:c r="B145" s="9" t="n">
+      <x:c r="B145" s="10" t="n">
         <x:v>46166</x:v>
       </x:c>
       <x:c r="C145" s="9" t="str">
@@ -4955,7 +4961,7 @@
       <x:c r="A146" s="9" t="n">
         <x:v>1145</x:v>
       </x:c>
-      <x:c r="B146" s="9" t="n">
+      <x:c r="B146" s="10" t="n">
         <x:v>46114</x:v>
       </x:c>
       <x:c r="C146" s="9" t="str">
@@ -4987,7 +4993,7 @@
       <x:c r="A147" s="9" t="n">
         <x:v>1146</x:v>
       </x:c>
-      <x:c r="B147" s="9" t="n">
+      <x:c r="B147" s="10" t="n">
         <x:v>46082</x:v>
       </x:c>
       <x:c r="C147" s="9" t="str">
@@ -5019,7 +5025,7 @@
       <x:c r="A148" s="9" t="n">
         <x:v>1147</x:v>
       </x:c>
-      <x:c r="B148" s="9" t="n">
+      <x:c r="B148" s="10" t="n">
         <x:v>46097</x:v>
       </x:c>
       <x:c r="C148" s="9" t="str">
@@ -5051,7 +5057,7 @@
       <x:c r="A149" s="9" t="n">
         <x:v>1148</x:v>
       </x:c>
-      <x:c r="B149" s="9" t="n">
+      <x:c r="B149" s="10" t="n">
         <x:v>46044</x:v>
       </x:c>
       <x:c r="C149" s="9" t="str">
@@ -5083,7 +5089,7 @@
       <x:c r="A150" s="9" t="n">
         <x:v>1149</x:v>
       </x:c>
-      <x:c r="B150" s="9" t="n">
+      <x:c r="B150" s="10" t="n">
         <x:v>46064</x:v>
       </x:c>
       <x:c r="C150" s="9" t="str">
@@ -5115,7 +5121,7 @@
       <x:c r="A151" s="9" t="n">
         <x:v>1150</x:v>
       </x:c>
-      <x:c r="B151" s="9" t="n">
+      <x:c r="B151" s="10" t="n">
         <x:v>46130</x:v>
       </x:c>
       <x:c r="C151" s="9" t="str">
@@ -5147,7 +5153,7 @@
       <x:c r="A152" s="9" t="n">
         <x:v>1151</x:v>
       </x:c>
-      <x:c r="B152" s="9" t="n">
+      <x:c r="B152" s="10" t="n">
         <x:v>46167</x:v>
       </x:c>
       <x:c r="C152" s="9" t="str">
@@ -5179,7 +5185,7 @@
       <x:c r="A153" s="9" t="n">
         <x:v>1152</x:v>
       </x:c>
-      <x:c r="B153" s="9" t="n">
+      <x:c r="B153" s="10" t="n">
         <x:v>46099</x:v>
       </x:c>
       <x:c r="C153" s="9" t="str">
@@ -5211,7 +5217,7 @@
       <x:c r="A154" s="9" t="n">
         <x:v>1153</x:v>
       </x:c>
-      <x:c r="B154" s="9" t="n">
+      <x:c r="B154" s="10" t="n">
         <x:v>46133</x:v>
       </x:c>
       <x:c r="C154" s="9" t="str">
@@ -5243,7 +5249,7 @@
       <x:c r="A155" s="9" t="n">
         <x:v>1154</x:v>
       </x:c>
-      <x:c r="B155" s="9" t="n">
+      <x:c r="B155" s="10" t="n">
         <x:v>46078</x:v>
       </x:c>
       <x:c r="C155" s="9" t="str">
@@ -5275,7 +5281,7 @@
       <x:c r="A156" s="9" t="n">
         <x:v>1155</x:v>
       </x:c>
-      <x:c r="B156" s="9" t="n">
+      <x:c r="B156" s="10" t="n">
         <x:v>46097</x:v>
       </x:c>
       <x:c r="C156" s="9" t="str">
@@ -5307,7 +5313,7 @@
       <x:c r="A157" s="9" t="n">
         <x:v>1156</x:v>
       </x:c>
-      <x:c r="B157" s="9" t="n">
+      <x:c r="B157" s="10" t="n">
         <x:v>46045</x:v>
       </x:c>
       <x:c r="C157" s="9" t="str">
@@ -5339,7 +5345,7 @@
       <x:c r="A158" s="9" t="n">
         <x:v>1157</x:v>
       </x:c>
-      <x:c r="B158" s="9" t="n">
+      <x:c r="B158" s="10" t="n">
         <x:v>46089</x:v>
       </x:c>
       <x:c r="C158" s="9" t="str">
@@ -5371,7 +5377,7 @@
       <x:c r="A159" s="9" t="n">
         <x:v>1158</x:v>
       </x:c>
-      <x:c r="B159" s="9" t="n">
+      <x:c r="B159" s="10" t="n">
         <x:v>46065</x:v>
       </x:c>
       <x:c r="C159" s="9" t="str">
@@ -5403,7 +5409,7 @@
       <x:c r="A160" s="9" t="n">
         <x:v>1159</x:v>
       </x:c>
-      <x:c r="B160" s="9" t="n">
+      <x:c r="B160" s="10" t="n">
         <x:v>46116</x:v>
       </x:c>
       <x:c r="C160" s="9" t="str">
@@ -5435,7 +5441,7 @@
       <x:c r="A161" s="9" t="n">
         <x:v>1160</x:v>
       </x:c>
-      <x:c r="B161" s="9" t="n">
+      <x:c r="B161" s="10" t="n">
         <x:v>46070</x:v>
       </x:c>
       <x:c r="C161" s="9" t="str">
@@ -5466,7 +5472,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re27eb392bba0494c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R630aa278d0ac4174"/>
   </x:tableParts>
 </x:worksheet>
 </file>